--- a/docs/StructureDefinition-RetinaObservation.xlsx
+++ b/docs/StructureDefinition-RetinaObservation.xlsx
@@ -30,19 +30,19 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.1</t>
+    <t>0.1.2</t>
   </si>
   <si>
     <t>Name</t>
   </si>
   <si>
-    <t>HelseSorOstRetinaObservation</t>
+    <t>DIPSRetinaIntegrationObservation</t>
   </si>
   <si>
     <t>Title</t>
   </si>
   <si>
-    <t>Observation for Retinascreening</t>
+    <t>Observation for retina screening</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-07T21:19:45+02:00</t>
+    <t>2025-10-19T20:08:40+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-RetinaObservation.xlsx
+++ b/docs/StructureDefinition-RetinaObservation.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.2</t>
+    <t>0.1.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-19T20:08:40+02:00</t>
+    <t>2025-10-31T08:54:10+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
